--- a/从零开始学Slots/从零开始学Slots-29-基础篇-Megaways6+1.xlsx
+++ b/从零开始学Slots/从零开始学Slots-29-基础篇-Megaways6+1.xlsx
@@ -10035,6 +10035,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N209" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -10958,5 +10961,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N91" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>